--- a/plantillas/plantillaEmulsion.xlsx
+++ b/plantillas/plantillaEmulsion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jejcl-my.sharepoint.com/personal/asalinasfre_jej_cl/Documents/CC650 JEJ/02. Carguío y Vibraciones/364.- Z-48 C41-43 3ra fase Esm NT-309/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D79D6EE-BFA2-4EAC-969D-27408897963A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0418A61-3B1B-45C1-8BFA-D611DA9BE88E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
